--- a/artfynd/A 1176-2024 artfynd.xlsx
+++ b/artfynd/A 1176-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1176-2024 artfynd.xlsx
+++ b/artfynd/A 1176-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114572151</v>
+        <v>114572136</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570207</v>
+        <v>570200</v>
       </c>
       <c r="R2" t="n">
-        <v>6425443</v>
+        <v>6425455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,12 +787,7 @@
         <v>114572140</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114572136</v>
+        <v>114572151</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570200</v>
+        <v>570207</v>
       </c>
       <c r="R4" t="n">
-        <v>6425455</v>
+        <v>6425443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,6 +999,126 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>95484381</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hackenäs V, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570168</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6425543</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Sven Halling, Ann Newsome</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
